--- a/BVSimulationFiles/77.xlsx
+++ b/BVSimulationFiles/77.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00195487002111175</v>
+        <v>0.0039097400422235</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001901152121576973</v>
+        <v>0.003802304243153946</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001840805138985433</v>
+        <v>0.003681610277970866</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001775500477757205</v>
+        <v>0.00355100095551441</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001706658389263771</v>
+        <v>0.003413316778527542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00163548001180995</v>
+        <v>0.0032709600236199</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001562975643351482</v>
+        <v>0.003125951286702964</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001489989668724343</v>
+        <v>0.002979979337448686</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001417222517460815</v>
+        <v>0.00283444503492163</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001345249987403658</v>
+        <v>0.002690499974807316</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001274540232800112</v>
+        <v>0.002549080465600224</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001205468682910673</v>
+        <v>0.002410937365821346</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001138331127998369</v>
+        <v>0.002276662255996738</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00107335518350923</v>
+        <v>0.00214671036701846</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001010710319987814</v>
+        <v>0.002021420639975628</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009505166255005823</v>
+        <v>0.001901033251001165</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008928524488024497</v>
+        <v>0.001785704897604899</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008377610549428472</v>
+        <v>0.001675522109885694</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007852564102564102</v>
+        <v>0.00157051282051282</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00195487002111175</v>
+        <v>0.0039097400422235</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001901152121576973</v>
+        <v>0.003802304243153946</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001840805138985433</v>
+        <v>0.003681610277970866</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001775500477757205</v>
+        <v>0.00355100095551441</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001706658389263771</v>
+        <v>0.003413316778527542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00163548001180995</v>
+        <v>0.0032709600236199</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001562975643351482</v>
+        <v>0.003125951286702964</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001489989668724343</v>
+        <v>0.002979979337448686</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001417222517460815</v>
+        <v>0.00283444503492163</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001345249987403658</v>
+        <v>0.002690499974807316</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001274540232800112</v>
+        <v>0.002549080465600224</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001205468682910673</v>
+        <v>0.002410937365821346</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001138331127998369</v>
+        <v>0.002276662255996738</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00107335518350923</v>
+        <v>0.00214671036701846</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001010710319987814</v>
+        <v>0.002021420639975628</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0009505166255005823</v>
+        <v>0.001901033251001165</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008928524488024497</v>
+        <v>0.001785704897604899</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008377610549428472</v>
+        <v>0.001675522109885694</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007852564102564102</v>
+        <v>0.00157051282051282</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/77.xlsx
+++ b/BVSimulationFiles/77.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004</v>
+        <v>0.04</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0039097400422235</v>
+        <v>0.039097400422235</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003802304243153946</v>
+        <v>0.03802304243153946</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003681610277970866</v>
+        <v>0.03681610277970866</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00355100095551441</v>
+        <v>0.0355100095551441</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003413316778527542</v>
+        <v>0.03413316778527542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0032709600236199</v>
+        <v>0.032709600236199</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003125951286702964</v>
+        <v>0.03125951286702964</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002979979337448686</v>
+        <v>0.02979979337448686</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00283444503492163</v>
+        <v>0.0283444503492163</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002690499974807316</v>
+        <v>0.02690499974807316</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002549080465600224</v>
+        <v>0.02549080465600224</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002410937365821346</v>
+        <v>0.02410937365821346</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002276662255996738</v>
+        <v>0.02276662255996738</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00214671036701846</v>
+        <v>0.0214671036701846</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002021420639975628</v>
+        <v>0.02021420639975628</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001901033251001165</v>
+        <v>0.01901033251001165</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001785704897604899</v>
+        <v>0.01785704897604899</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001675522109885694</v>
+        <v>0.01675522109885694</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00157051282051282</v>
+        <v>0.0157051282051282</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.004</v>
+        <v>0.04</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0039097400422235</v>
+        <v>0.039097400422235</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003802304243153946</v>
+        <v>0.03802304243153946</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003681610277970866</v>
+        <v>0.03681610277970866</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00355100095551441</v>
+        <v>0.0355100095551441</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003413316778527542</v>
+        <v>0.03413316778527542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0032709600236199</v>
+        <v>0.032709600236199</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003125951286702964</v>
+        <v>0.03125951286702964</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002979979337448686</v>
+        <v>0.02979979337448686</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00283444503492163</v>
+        <v>0.0283444503492163</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002690499974807316</v>
+        <v>0.02690499974807316</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002549080465600224</v>
+        <v>0.02549080465600224</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002410937365821346</v>
+        <v>0.02410937365821346</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002276662255996738</v>
+        <v>0.02276662255996738</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00214671036701846</v>
+        <v>0.0214671036701846</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002021420639975628</v>
+        <v>0.02021420639975628</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001901033251001165</v>
+        <v>0.01901033251001165</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001785704897604899</v>
+        <v>0.01785704897604899</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001675522109885694</v>
+        <v>0.01675522109885694</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00157051282051282</v>
+        <v>0.0157051282051282</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/77.xlsx
+++ b/BVSimulationFiles/77.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,61 +421,31 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.05646263157894737</v>
+        <v>0.03699275862068965</v>
       </c>
       <c r="D1" t="n">
-        <v>0.1129252631578947</v>
+        <v>0.07398551724137931</v>
       </c>
       <c r="E1" t="n">
-        <v>0.1693878947368421</v>
+        <v>0.1109782758620689</v>
       </c>
       <c r="F1" t="n">
-        <v>0.2258505263157895</v>
+        <v>0.1479710344827586</v>
       </c>
       <c r="G1" t="n">
-        <v>0.2823131578947368</v>
+        <v>0.1849637931034482</v>
       </c>
       <c r="H1" t="n">
-        <v>0.3387757894736842</v>
+        <v>0.2219565517241379</v>
       </c>
       <c r="I1" t="n">
-        <v>0.3952384210526316</v>
+        <v>0.2589493103448275</v>
       </c>
       <c r="J1" t="n">
-        <v>0.4517010526315789</v>
+        <v>0.2959420689655172</v>
       </c>
       <c r="K1" t="n">
-        <v>0.5081636842105263</v>
-      </c>
-      <c r="L1" t="n">
-        <v>0.5646263157894736</v>
-      </c>
-      <c r="M1" t="n">
-        <v>0.621088947368421</v>
-      </c>
-      <c r="N1" t="n">
-        <v>0.6775515789473684</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.7340142105263158</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.7904768421052631</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.8469394736842105</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.9034021052631579</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.9598647368421053</v>
-      </c>
-      <c r="T1" t="n">
-        <v>1.016327368421053</v>
-      </c>
-      <c r="U1" t="n">
-        <v>1.07279</v>
+        <v>0.3329348275862068</v>
       </c>
     </row>
     <row r="2">
@@ -483,64 +453,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04</v>
+        <v>0.1018834840915505</v>
       </c>
       <c r="C2" t="n">
-        <v>0.039097400422235</v>
+        <v>0.1042646890861068</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03802304243153946</v>
+        <v>0.1046471986339883</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03681610277970866</v>
+        <v>0.1034717024476137</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0355100095551441</v>
+        <v>0.1011024611659552</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03413316778527542</v>
+        <v>0.09783923791714423</v>
       </c>
       <c r="H2" t="n">
-        <v>0.032709600236199</v>
+        <v>0.09392747460726829</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03125951286702964</v>
+        <v>0.08956696147586587</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02979979337448686</v>
+        <v>0.08491921419224278</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0283444503492163</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.02690499974807316</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.02549080465600224</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.02410937365821346</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.02276662255996738</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.0214671036701846</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.02021420639975628</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.01901033251001165</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.01785704897604899</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.01675522109885694</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.0157051282051282</v>
+        <v>0.08011374313263142</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +488,34 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04</v>
+        <v>0.1018834840915505</v>
       </c>
       <c r="C3" t="n">
-        <v>0.039097400422235</v>
+        <v>0.1042646890861068</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03802304243153946</v>
+        <v>0.1046471986339883</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03681610277970866</v>
+        <v>0.1034717024476137</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0355100095551441</v>
+        <v>0.1011024611659552</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03413316778527542</v>
+        <v>0.09783923791714423</v>
       </c>
       <c r="H3" t="n">
-        <v>0.032709600236199</v>
+        <v>0.09392747460726829</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03125951286702964</v>
+        <v>0.08956696147586587</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02979979337448686</v>
+        <v>0.08491921419224278</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0283444503492163</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.02690499974807316</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.02549080465600224</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.02410937365821346</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.02276662255996738</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.0214671036701846</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.02021420639975628</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.01901033251001165</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.01785704897604899</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.01675522109885694</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.0157051282051282</v>
+        <v>0.08011374313263142</v>
       </c>
     </row>
   </sheetData>
